--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKSchwangerschaftsstatus.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKSchwangerschaftsstatus.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$85</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3248" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3288" uniqueCount="563">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-23</t>
+    <t>2025-12-11</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1211,7 +1211,7 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>Bedeutung: Erfasster Wert der Observation.</t>
+    <t>**Begründung Must-Support:** Erfasster Wert der Observation.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -1246,10 +1246,26 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
+    <t>Actual result</t>
+  </si>
+  <si>
     <t>Motivation: Harmonisierung mit KBV (KBV_PR_Base_RelatedPerson)</t>
   </si>
   <si>
     <t>https://gematik.de/fhir/isik/ValueSet/SchwangerschaftsstatusVS</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueDateTime</t>
+  </si>
+  <si>
+    <t>valueDateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>**Begründung Must-Support:** Zeitpunktbezogene Lebenszustände (z. B. erwarteter Entbindungstermin) benötigen eine eindeutige Datumsangabe als Wert.</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2087,7 +2103,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP84"/>
+  <dimension ref="A1:AP85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
@@ -8068,13 +8084,13 @@
         <v>237</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="M50" t="s" s="2">
         <v>376</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O50" t="s" s="2">
         <v>378</v>
@@ -8106,7 +8122,7 @@
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>18</v>
@@ -8157,14 +8173,16 @@
         <v>385</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>18</v>
       </c>
@@ -8176,28 +8194,28 @@
         <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>237</v>
+        <v>393</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>18</v>
@@ -8222,13 +8240,13 @@
         <v>18</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>395</v>
+        <v>18</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>18</v>
@@ -8246,7 +8264,7 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -8255,7 +8273,7 @@
         <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>101</v>
@@ -8264,38 +8282,38 @@
         <v>18</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>18</v>
+        <v>382</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>188</v>
+        <v>383</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>18</v>
+        <v>385</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>400</v>
+        <v>18</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>18</v>
@@ -8310,16 +8328,16 @@
         <v>237</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>18</v>
@@ -8347,10 +8365,10 @@
         <v>147</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>18</v>
@@ -8368,16 +8386,16 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>18</v>
+        <v>402</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>101</v>
@@ -8386,31 +8404,31 @@
         <v>18</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>407</v>
+        <v>18</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>408</v>
+        <v>188</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>410</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>18</v>
+        <v>405</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8429,19 +8447,19 @@
         <v>18</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>412</v>
+        <v>237</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>18</v>
@@ -8466,13 +8484,13 @@
         <v>18</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>18</v>
+        <v>410</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>18</v>
+        <v>411</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>18</v>
@@ -8490,7 +8508,7 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -8508,27 +8526,27 @@
         <v>18</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>18</v>
+        <v>412</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>18</v>
+        <v>415</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8539,7 +8557,7 @@
         <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>18</v>
@@ -8551,18 +8569,20 @@
         <v>18</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>237</v>
+        <v>417</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="N54" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>18</v>
       </c>
@@ -8586,13 +8606,13 @@
         <v>18</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>155</v>
+        <v>18</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>423</v>
+        <v>18</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>424</v>
+        <v>18</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>18</v>
@@ -8610,13 +8630,13 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>18</v>
@@ -8628,27 +8648,27 @@
         <v>18</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>425</v>
+        <v>18</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>428</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8674,17 +8694,15 @@
         <v>237</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>18</v>
       </c>
@@ -8711,10 +8729,10 @@
         <v>155</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>18</v>
@@ -8732,7 +8750,7 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8750,27 +8768,27 @@
         <v>18</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>18</v>
+        <v>430</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>18</v>
+        <v>433</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8793,18 +8811,20 @@
         <v>18</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>439</v>
+        <v>237</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>18</v>
       </c>
@@ -8828,13 +8848,13 @@
         <v>18</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>18</v>
+        <v>155</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>18</v>
+        <v>439</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>18</v>
+        <v>440</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>18</v>
@@ -8852,7 +8872,7 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8870,27 +8890,27 @@
         <v>18</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>443</v>
+        <v>18</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>446</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8913,16 +8933,16 @@
         <v>18</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8972,7 +8992,7 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8990,27 +9010,27 @@
         <v>18</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9021,7 +9041,7 @@
         <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>18</v>
@@ -9033,20 +9053,18 @@
         <v>18</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>18</v>
       </c>
@@ -9094,45 +9112,45 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>462</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>18</v>
+        <v>457</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>18</v>
+        <v>460</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9143,7 +9161,7 @@
         <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>18</v>
@@ -9155,16 +9173,20 @@
         <v>18</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>103</v>
+        <v>462</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>104</v>
+        <v>463</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>18</v>
       </c>
@@ -9212,19 +9234,19 @@
         <v>18</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>106</v>
+        <v>461</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>18</v>
+        <v>467</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>18</v>
@@ -9233,10 +9255,10 @@
         <v>18</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>18</v>
+        <v>468</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>107</v>
+        <v>469</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>18</v>
@@ -9247,21 +9269,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>18</v>
@@ -9273,17 +9295,15 @@
         <v>18</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>18</v>
@@ -9332,19 +9352,19 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>18</v>
@@ -9367,14 +9387,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>468</v>
+        <v>109</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9387,26 +9407,24 @@
         <v>18</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K61" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>469</v>
+        <v>111</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>470</v>
+        <v>112</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O61" t="s" s="2">
-        <v>195</v>
-      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>18</v>
       </c>
@@ -9454,7 +9472,7 @@
         <v>18</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>471</v>
+        <v>117</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -9478,7 +9496,7 @@
         <v>18</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>18</v>
@@ -9496,26 +9514,26 @@
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>18</v>
+        <v>473</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>473</v>
+        <v>110</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>474</v>
@@ -9523,8 +9541,12 @@
       <c r="M62" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+      <c r="N62" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>18</v>
       </c>
@@ -9572,19 +9594,19 @@
         <v>18</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>476</v>
+        <v>18</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>18</v>
@@ -9593,10 +9615,10 @@
         <v>18</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>477</v>
+        <v>18</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>478</v>
+        <v>188</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>18</v>
@@ -9607,10 +9629,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9633,13 +9655,13 @@
         <v>18</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9690,7 +9712,7 @@
         <v>18</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9699,7 +9721,7 @@
         <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>101</v>
@@ -9711,10 +9733,10 @@
         <v>18</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>18</v>
@@ -9725,10 +9747,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9751,20 +9773,16 @@
         <v>18</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>237</v>
+        <v>478</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N64" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="O64" t="s" s="2">
-        <v>487</v>
-      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>18</v>
       </c>
@@ -9788,13 +9806,13 @@
         <v>18</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>169</v>
+        <v>18</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>488</v>
+        <v>18</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>489</v>
+        <v>18</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>18</v>
@@ -9812,7 +9830,7 @@
         <v>18</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -9821,7 +9839,7 @@
         <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>18</v>
+        <v>481</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>101</v>
@@ -9830,13 +9848,13 @@
         <v>18</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>490</v>
+        <v>18</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>409</v>
+        <v>487</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>18</v>
@@ -9847,10 +9865,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9861,7 +9879,7 @@
         <v>77</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>18</v>
@@ -9876,16 +9894,16 @@
         <v>237</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>18</v>
@@ -9910,13 +9928,13 @@
         <v>18</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>18</v>
@@ -9934,13 +9952,13 @@
         <v>18</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>18</v>
@@ -9952,13 +9970,13 @@
         <v>18</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>18</v>
@@ -9969,10 +9987,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9983,7 +10001,7 @@
         <v>77</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>18</v>
@@ -9995,17 +10013,19 @@
         <v>18</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>18</v>
@@ -10030,13 +10050,13 @@
         <v>18</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>18</v>
+        <v>155</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>18</v>
+        <v>502</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>18</v>
+        <v>503</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>18</v>
@@ -10054,13 +10074,13 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>18</v>
@@ -10072,13 +10092,13 @@
         <v>18</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>18</v>
+        <v>495</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>18</v>
+        <v>496</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>504</v>
+        <v>414</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>18</v>
@@ -10089,10 +10109,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10115,7 +10135,7 @@
         <v>18</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>103</v>
+        <v>505</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>506</v>
@@ -10124,7 +10144,9 @@
         <v>507</v>
       </c>
       <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>18</v>
       </c>
@@ -10172,7 +10194,7 @@
         <v>18</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -10193,10 +10215,10 @@
         <v>18</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>477</v>
+        <v>18</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>18</v>
@@ -10205,12 +10227,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10224,16 +10246,16 @@
         <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>510</v>
+        <v>103</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>511</v>
@@ -10241,9 +10263,7 @@
       <c r="M68" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="N68" t="s" s="2">
-        <v>513</v>
-      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>18</v>
@@ -10292,13 +10312,13 @@
         <v>18</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>18</v>
@@ -10313,24 +10333,24 @@
         <v>18</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="AN68" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>516</v>
-      </c>
       <c r="B69" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10344,24 +10364,26 @@
         <v>89</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>103</v>
+        <v>515</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>104</v>
+        <v>516</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>18</v>
@@ -10410,19 +10432,19 @@
         <v>18</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>106</v>
+        <v>514</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>18</v>
@@ -10431,10 +10453,10 @@
         <v>18</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>18</v>
+        <v>519</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>107</v>
+        <v>520</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>18</v>
@@ -10445,21 +10467,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>18</v>
@@ -10471,17 +10493,15 @@
         <v>18</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>18</v>
@@ -10518,31 +10538,31 @@
         <v>18</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>114</v>
+        <v>18</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>116</v>
+        <v>18</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>18</v>
@@ -10563,44 +10583,44 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>519</v>
+        <v>111</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>300</v>
+        <v>112</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>520</v>
+        <v>113</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10638,31 +10658,31 @@
         <v>18</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>18</v>
+        <v>114</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>302</v>
+        <v>117</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>303</v>
+        <v>18</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>18</v>
@@ -10674,7 +10694,7 @@
         <v>18</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>18</v>
@@ -10683,12 +10703,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10696,13 +10716,13 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>18</v>
@@ -10711,16 +10731,16 @@
         <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>305</v>
+        <v>524</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>307</v>
+        <v>525</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10746,13 +10766,13 @@
         <v>18</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>308</v>
+        <v>18</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>309</v>
+        <v>18</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>18</v>
@@ -10770,7 +10790,7 @@
         <v>18</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -10779,7 +10799,7 @@
         <v>89</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>18</v>
+        <v>303</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>101</v>
@@ -10805,10 +10825,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10831,16 +10851,16 @@
         <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>198</v>
+        <v>131</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10866,13 +10886,13 @@
         <v>18</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>18</v>
+        <v>308</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>18</v>
+        <v>309</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>18</v>
@@ -10890,7 +10910,7 @@
         <v>18</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -10914,7 +10934,7 @@
         <v>18</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>316</v>
+        <v>188</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>18</v>
@@ -10925,10 +10945,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10951,16 +10971,16 @@
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>103</v>
+        <v>198</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11010,7 +11030,7 @@
         <v>18</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -11034,7 +11054,7 @@
         <v>18</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>188</v>
+        <v>316</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>18</v>
@@ -11045,10 +11065,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11059,7 +11079,7 @@
         <v>77</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>18</v>
@@ -11071,16 +11091,16 @@
         <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>525</v>
+        <v>103</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>526</v>
+        <v>318</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>527</v>
+        <v>319</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>528</v>
+        <v>320</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11130,13 +11150,13 @@
         <v>18</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>524</v>
+        <v>321</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>18</v>
@@ -11151,10 +11171,10 @@
         <v>18</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>514</v>
+        <v>18</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>529</v>
+        <v>188</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>18</v>
@@ -11165,10 +11185,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11191,7 +11211,7 @@
         <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>457</v>
+        <v>530</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>531</v>
@@ -11202,9 +11222,7 @@
       <c r="N76" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="O76" t="s" s="2">
-        <v>534</v>
-      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>18</v>
       </c>
@@ -11252,7 +11270,7 @@
         <v>18</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -11273,10 +11291,10 @@
         <v>18</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>18</v>
@@ -11287,10 +11305,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11301,7 +11319,7 @@
         <v>77</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>18</v>
@@ -11310,19 +11328,23 @@
         <v>18</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>103</v>
+        <v>462</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>104</v>
+        <v>536</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>537</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>18</v>
       </c>
@@ -11370,19 +11392,19 @@
         <v>18</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>106</v>
+        <v>535</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>18</v>
@@ -11391,10 +11413,10 @@
         <v>18</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>18</v>
+        <v>540</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>107</v>
+        <v>541</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>18</v>
@@ -11405,21 +11427,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>18</v>
@@ -11431,17 +11453,15 @@
         <v>18</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>18</v>
@@ -11490,19 +11510,19 @@
         <v>18</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>18</v>
@@ -11525,14 +11545,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>468</v>
+        <v>109</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11545,26 +11565,24 @@
         <v>18</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K79" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>469</v>
+        <v>111</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>470</v>
+        <v>112</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O79" t="s" s="2">
-        <v>195</v>
-      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>18</v>
       </c>
@@ -11612,7 +11630,7 @@
         <v>18</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>471</v>
+        <v>117</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -11636,7 +11654,7 @@
         <v>18</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>18</v>
@@ -11647,45 +11665,45 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>18</v>
+        <v>473</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J80" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>237</v>
+        <v>110</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>541</v>
+        <v>474</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>542</v>
+        <v>475</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>543</v>
+        <v>113</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>18</v>
@@ -11710,13 +11728,13 @@
         <v>18</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>155</v>
+        <v>18</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>252</v>
+        <v>18</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>253</v>
+        <v>18</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>18</v>
@@ -11734,34 +11752,34 @@
         <v>18</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>540</v>
+        <v>476</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>256</v>
+        <v>18</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>257</v>
+        <v>188</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>258</v>
+        <v>18</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>18</v>
@@ -11780,7 +11798,7 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>89</v>
@@ -11795,19 +11813,19 @@
         <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>548</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>378</v>
+        <v>250</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>18</v>
@@ -11832,13 +11850,13 @@
         <v>18</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>18</v>
+        <v>155</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>18</v>
+        <v>252</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>18</v>
+        <v>253</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>18</v>
@@ -11859,7 +11877,7 @@
         <v>545</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>89</v>
@@ -11877,16 +11895,16 @@
         <v>549</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>383</v>
+        <v>256</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>384</v>
+        <v>257</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>18</v>
+        <v>258</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>385</v>
+        <v>18</v>
       </c>
     </row>
     <row r="82" hidden="true">
@@ -11914,22 +11932,22 @@
         <v>18</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>237</v>
+        <v>551</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>552</v>
+        <v>376</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>553</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>18</v>
@@ -11954,13 +11972,13 @@
         <v>18</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>395</v>
+        <v>18</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>18</v>
@@ -11987,7 +12005,7 @@
         <v>89</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>397</v>
+        <v>18</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>101</v>
@@ -11996,38 +12014,38 @@
         <v>18</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>18</v>
+        <v>554</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>188</v>
+        <v>383</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>18</v>
+        <v>385</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>400</v>
+        <v>18</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>18</v>
@@ -12042,16 +12060,16 @@
         <v>237</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>401</v>
+        <v>556</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>402</v>
+        <v>557</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>403</v>
+        <v>558</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>18</v>
@@ -12079,10 +12097,10 @@
         <v>147</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>18</v>
@@ -12100,16 +12118,16 @@
         <v>18</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>18</v>
+        <v>402</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>101</v>
@@ -12118,31 +12136,31 @@
         <v>18</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>407</v>
+        <v>18</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>408</v>
+        <v>188</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>410</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>18</v>
+        <v>405</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12161,19 +12179,19 @@
         <v>18</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>18</v>
+        <v>237</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>556</v>
+        <v>406</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>557</v>
+        <v>407</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>460</v>
+        <v>408</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>461</v>
+        <v>409</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>18</v>
@@ -12198,13 +12216,13 @@
         <v>18</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>18</v>
+        <v>410</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>18</v>
+        <v>411</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>18</v>
@@ -12222,7 +12240,7 @@
         <v>18</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
@@ -12240,23 +12258,145 @@
         <v>18</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>18</v>
+        <v>412</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>463</v>
+        <v>413</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>464</v>
+        <v>414</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP84" t="s" s="2">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP85" t="s" s="2">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP84">
+  <autoFilter ref="A1:AP85">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12266,7 +12406,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI83">
+  <conditionalFormatting sqref="A2:AI84">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKSchwangerschaftsstatus.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKSchwangerschaftsstatus.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-11</t>
+    <t>2025-12-17</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKSchwangerschaftsstatus.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKSchwangerschaftsstatus.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.1</t>
+    <t>0.0.1-rc</t>
   </si>
   <si>
     <t>Name</t>
